--- a/r4-ELGA-e-Diagnose-4-lesende-zugriffe-get-vs-operation/StructureDefinition-at-elga-ediag-ext-entered-in-error.xlsx
+++ b/r4-ELGA-e-Diagnose-4-lesende-zugriffe-get-vs-operation/StructureDefinition-at-elga-ediag-ext-entered-in-error.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T06:56:37+00:00</t>
+    <t>2026-09-09T15:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -367,7 +367,7 @@
     <t>Extension.extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner) {https://fhir.hl7.at/elga/ediag/r4/StructureDefinition/at-elga-ediag-reference}
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner)
 </t>
   </si>
   <si>
